--- a/ZumNet.Web/Content/Forms/IMPORT/FORM_PURCHASEUCF.xlsx
+++ b/ZumNet.Web/Content/Forms/IMPORT/FORM_PURCHASEUCF.xlsx
@@ -1,25 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\새 폴더 (3)\새 폴더\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\09 사업\10 유지보수\01 크레신\2508 신규ERP연동 외\엑셀가져오기\DRM 해제\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359BBC41-34AF-4898-BDBE-82251E815F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="170" windowWidth="16160" windowHeight="11990"/>
+    <workbookView xWindow="3960" yWindow="3615" windowWidth="24870" windowHeight="16005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
   <si>
     <t>품번</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -29,10 +46,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>BPA</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>적용시점</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -41,54 +54,60 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>EMB-SSG731STWA</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>CMH-0473LUT-WA</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>13646</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>13646-B-00002</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>모델번호</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EMB-SSG731STWA</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>CMK-0608ZNX-WA</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>가단가</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>법인명</t>
+    <t>사업장</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>CT</t>
+    <t>모델명</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>CT</t>
+    <t>UOM</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>VH</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>220790</t>
+  </si>
+  <si>
+    <t>EPP-EKO001STFOT</t>
+  </si>
+  <si>
+    <t>CJZ-0011ZZZ-OA</t>
+  </si>
+  <si>
+    <t>CJZ-0011ZZZ-PB</t>
+  </si>
+  <si>
+    <t>CJZ-0011ZZZ-AD</t>
+  </si>
+  <si>
+    <t>222</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>333</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>111</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0.00000_);[Red]\(#,##0.00000\)"/>
   </numFmts>
@@ -770,9 +789,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -810,9 +829,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -847,7 +866,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -882,7 +901,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1055,90 +1074,120 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="16.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.08203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="12.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="2" max="2" width="16.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="12.375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3">
+        <v>46023</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="3">
+        <v>46023</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="4">
-        <v>4.4110000000000003E-2</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="3">
-        <v>41740</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.14276</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="3">
-        <v>41740</v>
+      <c r="G4" s="3">
+        <v>46023</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
